--- a/Dashboard_v2/src/Infrastructure/Templates/AnexoEventosCientificos.xlsx
+++ b/Dashboard_v2/src/Infrastructure/Templates/AnexoEventosCientificos.xlsx
@@ -6,14 +6,20 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Eventos y actividades" sheetId="1" r:id="rId2"/>
+    <x:sheet name="1. Eventos Internacionales" sheetId="1" r:id="rId2"/>
+    <x:sheet name="2. Eventos Nacionales" sheetId="2" r:id="rId3"/>
+    <x:sheet name="3. Eventos Coauspiciados" sheetId="3" r:id="rId4"/>
+    <x:sheet name="4. Actividades en la UH" sheetId="4" r:id="rId5"/>
+    <x:sheet name="5. Ponencias - Resumen" sheetId="5" r:id="rId6"/>
+    <x:sheet name="6. Conferencias Magistrales" sheetId="6" r:id="rId7"/>
+    <x:sheet name="7. Datos de Ponencias" sheetId="7" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="EventosInternacionales">'Eventos y actividades'!$A$6:$C$7</x:definedName>
-    <x:definedName name="EventosNacionales">'Eventos y actividades'!$A$15:$B$16</x:definedName>
-    <x:definedName name="EventosCoauspiciados">'Eventos y actividades'!$A$23:$D$24</x:definedName>
-    <x:definedName name="ActividadesCientificasUH">'Eventos y actividades'!$A$32:$A$33</x:definedName>
-    <x:definedName name="DatosPonencias">'Eventos y actividades'!$A$60:$D$61</x:definedName>
+    <x:definedName name="EventosInternacionales">'1. Eventos Internacionales'!$A$2:$C$3</x:definedName>
+    <x:definedName name="EventosNacionales">'2. Eventos Nacionales'!$A$2:$B$3</x:definedName>
+    <x:definedName name="EventosCoauspiciados">'3. Eventos Coauspiciados'!$A$2:$D$3</x:definedName>
+    <x:definedName name="ActividadesCientificasUH">'4. Actividades en la UH'!$A$2:$A$3</x:definedName>
+    <x:definedName name="DatosPonencias">'7. Datos de Ponencias'!$A$2:$D$3</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -22,16 +28,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Anexo 3.  EVENTOS Y ACTIVIDADES CIENTIFICAS BALANCE 2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.  Eventos cientificos internacionales (en el extranjero o en Cuba) en los que profesores o investigadores del area han tenido cualquier tipo de participacion:</x:t>
-  </x:si>
-  <x:si>
     <x:t>Nombre del evento internacional</x:t>
   </x:si>
   <x:si>
-    <x:t>Pais, si fue en el extranjero</x:t>
+    <x:t>País, si fue en el extranjero</x:t>
   </x:si>
   <x:si>
     <x:t>En Cuba</x:t>
@@ -49,13 +49,10 @@
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2. Eventos cientificos nacionales (en Cuba) en los que profesores o investigadores del area han tenido cualquier tipo de participacion:</x:t>
-  </x:si>
-  <x:si>
     <x:t>Nombre del evento nacional en Cuba</x:t>
   </x:si>
   <x:si>
-    <x:t>Institucion que lo organizo</x:t>
+    <x:t>Institución que lo organizó</x:t>
   </x:si>
   <x:si>
     <x:t>{{item.NombreEventoNacional}}</x:t>
@@ -64,13 +61,10 @@
     <x:t>{{item.InstitucionQueLoOrganizo}}</x:t>
   </x:si>
   <x:si>
-    <x:t>3. Eventos cientificos coauspiciados por el area:</x:t>
-  </x:si>
-  <x:si>
     <x:t>Evento coauspiciado</x:t>
   </x:si>
   <x:si>
-    <x:t>Institucion externa a la UH responsable del evento</x:t>
+    <x:t>Institución externa a la UH responsable del evento</x:t>
   </x:si>
   <x:si>
     <x:t>Internacional</x:t>
@@ -91,28 +85,22 @@
     <x:t>{{item.Nacional}}</x:t>
   </x:si>
   <x:si>
-    <x:t>4. Actividades cientificas organizadas por el area en la UH:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Actividad cientifica</x:t>
+    <x:t>Actividad científica</x:t>
   </x:si>
   <x:si>
     <x:t>{{item.ActividadCientifica}}</x:t>
   </x:si>
   <x:si>
-    <x:t>5. Ponencias presentadas:</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cantidad de ponencias</x:t>
   </x:si>
   <x:si>
-    <x:t>Cantidad donde 1er autor es del area</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cantidad con autores de otras areas de la UH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>En eventos internacionales en extranjero</x:t>
+    <x:t>Cantidad donde 1er autor es del área</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cantidad con autores de otras áreas de la UH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>En eventos internacionales en el extranjero</x:t>
   </x:si>
   <x:si>
     <x:t>{{PonenciasInternacionalesExtranjero}}</x:t>
@@ -130,7 +118,7 @@
     <x:t>{{PonenciasNacionalesCuba}}</x:t>
   </x:si>
   <x:si>
-    <x:t>En actividades cientificas celebradas en la UH</x:t>
+    <x:t>En actividades científicas celebradas en la UH</x:t>
   </x:si>
   <x:si>
     <x:t>{{PonenciasActividadesUH}}</x:t>
@@ -142,9 +130,6 @@
     <x:t>{{PonenciasTotal}}</x:t>
   </x:si>
   <x:si>
-    <x:t>6. Conferencias magistrales impartidas:</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cantidad</x:t>
   </x:si>
   <x:si>
@@ -154,19 +139,16 @@
     <x:t>En instituciones cubanas</x:t>
   </x:si>
   <x:si>
-    <x:t>7. Datos de ponencias presentadas en eventos y actividades cientificas.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Nombre de la ponencia</x:t>
   </x:si>
   <x:si>
     <x:t>Nombre de autores</x:t>
   </x:si>
   <x:si>
-    <x:t>Nombre del evento o actividad cientifica</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pais de celebracion</x:t>
+    <x:t>Nombre del evento o actividad científica</x:t>
+  </x:si>
+  <x:si>
+    <x:t>País de celebración</x:t>
   </x:si>
   <x:si>
     <x:t>{{item.NombrePonencia}}</x:t>
@@ -179,21 +161,6 @@
   </x:si>
   <x:si>
     <x:t>{{item.PaisDeCelebracion}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NOTAS:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- El anexo se entrega en Word en el mismo modelo del anexo.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Informar solo lo que se pide en cada punto.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Cualquier duda comunicarse con Manuel Alvarez (DCT) por WhatsApp 53026650.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Los apartados 3 y 4 se mantienen para llenado manual: el sistema no modela eventos coauspiciados ni actividades cientificas internas en la UH.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -264,11 +231,8 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -278,13 +242,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -304,10 +264,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -606,385 +562,413 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D71"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="43.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="50.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="18.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4" ht="22.5" customHeight="1">
+    <x:row r="1" spans="1:3">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B3"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="55.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="40.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:D3"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="2" width="38.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="4" width="16.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
+      <x:c r="A3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:A3"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="70.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:1">
+      <x:c r="A2" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:1">
+      <x:c r="A3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:D6"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="52.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+    </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C3" s="4"/>
+      <x:c r="D3" s="4"/>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C4" s="4"/>
+      <x:c r="D4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C5" s="4"/>
+      <x:c r="D5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
-      <x:c r="A7" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
-      <x:c r="A12" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="1"/>
-      <x:c r="C12" s="1"/>
-      <x:c r="D12" s="1"/>
-    </x:row>
-    <x:row r="14" spans="1:4">
-      <x:c r="A14" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:4">
-      <x:c r="A15" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:4">
-      <x:c r="A16" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B16" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:4">
-      <x:c r="A20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B20" s="1"/>
-      <x:c r="C20" s="1"/>
-      <x:c r="D20" s="1"/>
-    </x:row>
-    <x:row r="22" spans="1:4">
-      <x:c r="A22" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B22" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C22" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D22" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:4">
-      <x:c r="A23" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B23" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C23" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D23" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:4">
-      <x:c r="A24" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B24" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C24" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:4">
-      <x:c r="A29" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B29" s="1"/>
-      <x:c r="C29" s="1"/>
-      <x:c r="D29" s="1"/>
-    </x:row>
-    <x:row r="31" spans="1:4">
-      <x:c r="A31" s="2" t="s">
+      <x:c r="A6" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C6" s="4"/>
+      <x:c r="D6" s="4"/>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B8"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="52.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" spans="1:4">
-      <x:c r="A32" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:4">
-      <x:c r="A33" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:4">
-      <x:c r="A37" s="1" t="s">
+      <x:c r="B2" s="4"/>
+    </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B37" s="1"/>
-      <x:c r="C37" s="1"/>
-      <x:c r="D37" s="1"/>
-    </x:row>
-    <x:row r="39" spans="1:4">
-      <x:c r="A39" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B39" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C39" s="2" t="s">
+      <x:c r="B3" s="4"/>
+    </x:row>
+    <x:row r="4" spans="1:2">
+      <x:c r="A4" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D39" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:4">
-      <x:c r="A40" s="3" t="s">
+      <x:c r="B4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:2">
+      <x:c r="A5" s="2" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B40" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C40" s="5"/>
-      <x:c r="D40" s="5"/>
-    </x:row>
-    <x:row r="41" spans="1:4">
-      <x:c r="A41" s="3" t="s">
+      <x:c r="B5" s="4"/>
+    </x:row>
+    <x:row r="6" spans="1:2">
+      <x:c r="A6" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B6" s="4"/>
+    </x:row>
+    <x:row r="7" spans="1:2">
+      <x:c r="A7" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B7" s="4"/>
+    </x:row>
+    <x:row r="8" spans="1:2">
+      <x:c r="A8" s="5" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B41" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C41" s="5"/>
-      <x:c r="D41" s="5"/>
-    </x:row>
-    <x:row r="42" spans="1:4">
-      <x:c r="A42" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B42" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C42" s="5"/>
-      <x:c r="D42" s="5"/>
-    </x:row>
-    <x:row r="43" spans="1:4">
-      <x:c r="A43" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B43" s="4" t="s">
+      <x:c r="B8" s="4"/>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:D3"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="3" width="32.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C43" s="5"/>
-      <x:c r="D43" s="5"/>
-    </x:row>
-    <x:row r="44" spans="1:4">
-      <x:c r="A44" s="6" t="s">
+      <x:c r="B1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B44" s="2" t="s">
+      <x:c r="C1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C44" s="5"/>
-      <x:c r="D44" s="5"/>
-    </x:row>
-    <x:row r="47" spans="1:4">
-      <x:c r="A47" s="1" t="s">
+      <x:c r="D1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B47" s="1"/>
-      <x:c r="C47" s="1"/>
-      <x:c r="D47" s="1"/>
-    </x:row>
-    <x:row r="49" spans="1:4">
-      <x:c r="A49" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B49" s="2" t="s">
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="2" t="s">
         <x:v>41</x:v>
       </x:c>
-    </x:row>
-    <x:row r="50" spans="1:4">
-      <x:c r="A50" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B50" s="5"/>
-    </x:row>
-    <x:row r="51" spans="1:4">
-      <x:c r="A51" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B51" s="5"/>
-    </x:row>
-    <x:row r="52" spans="1:4">
-      <x:c r="A52" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B52" s="5"/>
-    </x:row>
-    <x:row r="53" spans="1:4">
-      <x:c r="A53" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B53" s="5"/>
-    </x:row>
-    <x:row r="54" spans="1:4">
-      <x:c r="A54" s="3" t="s">
+      <x:c r="B2" s="3" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B54" s="5"/>
-    </x:row>
-    <x:row r="55" spans="1:4">
-      <x:c r="A55" s="3" t="s">
+      <x:c r="C2" s="3" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B55" s="5"/>
-    </x:row>
-    <x:row r="56" spans="1:4">
-      <x:c r="A56" s="6" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B56" s="5"/>
-    </x:row>
-    <x:row r="58" spans="1:4">
-      <x:c r="A58" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B58" s="1"/>
-      <x:c r="C58" s="1"/>
-      <x:c r="D58" s="1"/>
-    </x:row>
-    <x:row r="59" spans="1:4">
-      <x:c r="A59" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B59" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C59" s="2" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D59" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:4">
-      <x:c r="A60" s="3" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B60" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C60" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D60" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:4">
-      <x:c r="A61" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B61" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C61" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D61" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:4">
-      <x:c r="A67" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:4">
-      <x:c r="A68" s="7" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:4">
-      <x:c r="A69" s="7" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:4">
-      <x:c r="A70" s="7" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:4">
-      <x:c r="A71" s="7" t="s">
-        <x:v>57</x:v>
+    </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="8">
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A3:D3"/>
-    <x:mergeCell ref="A12:D12"/>
-    <x:mergeCell ref="A20:D20"/>
-    <x:mergeCell ref="A29:D29"/>
-    <x:mergeCell ref="A37:D37"/>
-    <x:mergeCell ref="A47:D47"/>
-    <x:mergeCell ref="A58:D58"/>
-  </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
